--- a/data/CU_ARS_2026_crossing_t3_upload.xlsx
+++ b/data/CU_ARS_2026_crossing_t3_upload.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pth7\Documents\Intercrop JLJ\2026_winter\2026_winter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C190809-DF0B-465B-8BC7-561620CCE7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CED8FB6-AE00-46DC-8B02-7BC862E6E43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B270D39F-4B60-4F3E-B730-6EA7960E6E49}"/>
+    <workbookView xWindow="4416" yWindow="17280" windowWidth="21600" windowHeight="11100" xr2:uid="{B270D39F-4B60-4F3E-B730-6EA7960E6E49}"/>
   </bookViews>
   <sheets>
-    <sheet name="seed_set" sheetId="11" r:id="rId1"/>
-    <sheet name="crosses_upload" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
-    <sheet name="cross_target" sheetId="9" r:id="rId4"/>
-    <sheet name="plant_count" sheetId="4" r:id="rId5"/>
-    <sheet name="template" sheetId="5" r:id="rId6"/>
-    <sheet name="crosses" sheetId="6" r:id="rId7"/>
-    <sheet name="parents" sheetId="7" r:id="rId8"/>
-    <sheet name="seedlots" sheetId="1" r:id="rId9"/>
-    <sheet name="T3_trial_upload" sheetId="3" r:id="rId10"/>
-    <sheet name="accession" sheetId="2" r:id="rId11"/>
+    <sheet name="seed_lots" sheetId="12" r:id="rId1"/>
+    <sheet name="seed_set" sheetId="11" r:id="rId2"/>
+    <sheet name="crosses_upload" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId4"/>
+    <sheet name="cross_target" sheetId="9" r:id="rId5"/>
+    <sheet name="plant_count" sheetId="4" r:id="rId6"/>
+    <sheet name="template" sheetId="5" r:id="rId7"/>
+    <sheet name="crosses" sheetId="6" r:id="rId8"/>
+    <sheet name="parents" sheetId="7" r:id="rId9"/>
+    <sheet name="seedlots" sheetId="1" r:id="rId10"/>
+    <sheet name="T3_trial_upload" sheetId="3" r:id="rId11"/>
+    <sheet name="accession" sheetId="2" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="190">
   <si>
     <t>NC20-4551-UWON_2024-Entry_011</t>
   </si>
@@ -610,6 +611,105 @@
   </si>
   <si>
     <t>Number of Seeds</t>
+  </si>
+  <si>
+    <t>operator_name</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>box_name</t>
+  </si>
+  <si>
+    <t>Peter Hyde</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_1</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_6</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_4</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_3</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_5</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_2</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_7</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_8</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_9</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_10</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_11</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_12</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_19</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_22</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_F1_26</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_13</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_14</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_15</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_16</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_17</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_18</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_20</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_21</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_23</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_24</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_25</t>
+  </si>
+  <si>
+    <t>CU_ARS_2026_WOF_P_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seed from winter oat founder WOF crossing block winter 2025-2026.  Included F1 seed and parent seed from each individual parent used for crossing.  50 seed parent seedlots are estimates.  Seedlot naming  F1-1 is F1 seed tag 1  P-13 is parent seed tag 13. </t>
   </si>
 </sst>
 </file>
@@ -703,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -725,6 +825,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1059,566 +1162,742 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F5C7982-B0E1-4A02-9DE3-70BD1B3A4495}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D3D458-C49C-4FCF-A121-DF11B1313984}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" t="s">
         <v>70</v>
       </c>
-      <c r="B4">
+      <c r="C4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
       </c>
-      <c r="B6">
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
         <v>73</v>
       </c>
-      <c r="B7">
+      <c r="C7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="B8">
+      <c r="C8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" t="s">
         <v>75</v>
       </c>
-      <c r="B9">
+      <c r="C9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" t="s">
         <v>76</v>
       </c>
-      <c r="B10">
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" t="s">
         <v>77</v>
       </c>
-      <c r="B11">
+      <c r="C11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="B13">
+      <c r="C13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" t="s">
         <v>86</v>
       </c>
-      <c r="B20">
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>189</v>
+      </c>
+      <c r="F21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
+        <v>189</v>
+      </c>
+      <c r="F24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25">
+        <v>50</v>
+      </c>
+      <c r="E25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>188</v>
+      </c>
+      <c r="B28" t="s">
         <v>155</v>
       </c>
+      <c r="C28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CBFCDF-E2EC-4717-88DB-714DC6C8EBD4}">
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C40C38-D08F-4418-BDAD-3D404DA3F501}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="103.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" customWidth="1"/>
-    <col min="10" max="11" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="63.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="68.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2026</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="str">
-        <f>_xlfn.CONCAT(A2,"_",J2)</f>
-        <v>CU_ARS_2026_WOF_crossing_20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>20</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>2026</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H9" si="0">_xlfn.CONCAT(A3,"_",J3)</f>
-        <v>CU_ARS_2026_WOF_crossing_21</v>
-      </c>
-      <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="J3">
-        <v>21</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>2026</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_22</v>
-      </c>
-      <c r="I4" t="s">
         <v>9</v>
       </c>
-      <c r="J4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5">
-        <v>2026</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>23</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6">
-        <v>2026</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>24</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>2026</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_25</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8">
-        <v>2026</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D9">
-        <v>2026</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>33</v>
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="0"/>
-        <v>CU_ARS_2026_WOF_crossing_27</v>
-      </c>
-      <c r="I9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>27</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1627,16 +1906,388 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CBFCDF-E2EC-4717-88DB-714DC6C8EBD4}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="103.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="63.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="str">
+        <f>_xlfn.CONCAT(A2,"_",J2)</f>
+        <v>CU_ARS_2026_WOF_crossing_20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H9" si="0">_xlfn.CONCAT(A3,"_",J3)</f>
+        <v>CU_ARS_2026_WOF_crossing_21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>21</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>22</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>23</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>24</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>CU_ARS_2026_WOF_crossing_27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCE9D8C-A788-4420-9286-271D383FF2A9}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="103.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="103.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1647,7 +2298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1664,18 +2315,256 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F5C7982-B0E1-4A02-9DE3-70BD1B3A4495}">
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82900F6C-FB74-4428-974A-873F79F809BC}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="38.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -1692,7 +2581,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -1709,7 +2598,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1726,7 +2615,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1743,7 +2632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -1760,7 +2649,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -1777,7 +2666,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1794,7 +2683,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1811,7 +2700,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1828,7 +2717,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -1845,7 +2734,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -1862,7 +2751,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -1879,7 +2768,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -1896,7 +2785,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -1910,7 +2799,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -1924,7 +2813,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1938,7 +2827,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -1952,7 +2841,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -1966,7 +2855,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -1980,7 +2869,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -1997,7 +2886,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>147</v>
       </c>
@@ -2011,7 +2900,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -2025,7 +2914,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>149</v>
       </c>
@@ -2042,7 +2931,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -2056,7 +2945,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -2070,7 +2959,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>153</v>
       </c>
@@ -2084,7 +2973,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -2101,7 +2990,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>155</v>
       </c>
@@ -2121,21 +3010,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8C752EA-379D-4849-B4BF-29AE436EE7C8}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -2143,7 +3032,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2151,7 +3040,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -2159,7 +3048,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -2167,7 +3056,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -2175,7 +3064,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -2183,7 +3072,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -2191,12 +3080,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>107</v>
       </c>
@@ -2204,7 +3093,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>108</v>
       </c>
@@ -2212,12 +3101,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -2233,18 +3122,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2B4254-A6AC-4849-9D55-7D2BCA730195}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>143</v>
       </c>
@@ -2258,7 +3147,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2272,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2286,7 +3175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -2300,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -2314,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2328,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2342,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2354,92 +3243,6 @@
       </c>
       <c r="D8">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3181BD-E2DD-4DF5-855A-6D89D396FB6A}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2448,122 +3251,84 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF4CDA7-BE78-44CC-BBCC-1DA3922B297A}">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="43.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3181BD-E2DD-4DF5-855A-6D89D396FB6A}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>65</v>
+    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2572,21 +3337,145 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF4CDA7-BE78-44CC-BBCC-1DA3922B297A}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="43.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="57" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02367D02-24B8-4F83-954C-5CC186ECAD30}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -2603,7 +3492,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -2633,7 +3522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -2663,7 +3552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -2693,7 +3582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -2723,7 +3612,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -2753,7 +3642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -2783,7 +3672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -2813,7 +3702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -2843,7 +3732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -2873,7 +3762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -2897,7 +3786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -2927,7 +3816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -2957,7 +3846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -2980,7 +3869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3003,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -3026,7 +3915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -3049,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -3072,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3089,7 +3978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -3119,25 +4008,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DB5069-D2CF-43DD-A042-29E5C15CA244}">
   <dimension ref="A1:K43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>87</v>
       </c>
@@ -3172,7 +4061,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -3198,7 +4087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -3224,7 +4113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -3250,7 +4139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -3276,7 +4165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -3302,7 +4191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -3328,7 +4217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -3354,7 +4243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>105</v>
       </c>
@@ -3380,7 +4269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -3406,7 +4295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -3441,7 +4330,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>107</v>
       </c>
@@ -3467,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>108</v>
       </c>
@@ -3493,7 +4382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
@@ -3519,7 +4408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>110</v>
       </c>
@@ -3545,7 +4434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -3571,7 +4460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -3597,7 +4486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -3623,7 +4512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -3649,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -3675,7 +4564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -3701,7 +4590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -3727,7 +4616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -3753,7 +4642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -3779,7 +4668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -3805,7 +4694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -3831,7 +4720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -3857,7 +4746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -3883,7 +4772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3909,7 +4798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +4824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -3961,7 +4850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -3987,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>128</v>
       </c>
@@ -4013,7 +4902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>129</v>
       </c>
@@ -4039,7 +4928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>130</v>
       </c>
@@ -4065,7 +4954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -4091,7 +4980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -4117,7 +5006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -4143,7 +5032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -4169,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -4195,7 +5084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -4219,172 +5108,6 @@
       </c>
       <c r="K43">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C40C38-D08F-4418-BDAD-3D404DA3F501}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="2" max="2" width="68.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
